--- a/docs/assets/cases/selection.xlsx
+++ b/docs/assets/cases/selection.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="39">
   <si>
     <t>feature</t>
   </si>
@@ -37,67 +37,100 @@
     <t>description</t>
   </si>
   <si>
+    <t>main_score</t>
+  </si>
+  <si>
+    <t>champion</t>
+  </si>
+  <si>
+    <t>Dropped</t>
+  </si>
+  <si>
+    <t>Corr_Filter</t>
+  </si>
+  <si>
+    <t>Correlated with 'score_inverse'</t>
+  </si>
+  <si>
+    <t>constant</t>
+  </si>
+  <si>
+    <t>application</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Single Value (Mode)</t>
+  </si>
+  <si>
+    <t>sparse</t>
+  </si>
+  <si>
+    <t>High Missing</t>
+  </si>
+  <si>
+    <t>income</t>
+  </si>
+  <si>
+    <t>Rough_Scan</t>
+  </si>
+  <si>
+    <t>Low IV &amp; Low Lift</t>
+  </si>
+  <si>
     <t>income_copy</t>
   </si>
   <si>
-    <t>application</t>
-  </si>
-  <si>
-    <t>Dropped</t>
-  </si>
-  <si>
-    <t>Corr_Filter</t>
-  </si>
-  <si>
-    <t>Correlated with 'income'</t>
+    <t>aux_drift</t>
+  </si>
+  <si>
+    <t>challenger</t>
+  </si>
+  <si>
+    <t>Stability</t>
+  </si>
+  <si>
+    <t>High PSI (9.46)</t>
+  </si>
+  <si>
+    <t>aux_score</t>
+  </si>
+  <si>
+    <t>Selected</t>
+  </si>
+  <si>
+    <t>Independent</t>
   </si>
   <si>
     <t>score_inverse</t>
   </si>
   <si>
-    <t>champion</t>
-  </si>
-  <si>
-    <t>Correlated with 'main_score'</t>
-  </si>
-  <si>
-    <t>constant</t>
-  </si>
-  <si>
-    <t>Quality</t>
-  </si>
-  <si>
-    <t>Single Value (Mode)</t>
-  </si>
-  <si>
-    <t>sparse</t>
-  </si>
-  <si>
-    <t>High Missing</t>
-  </si>
-  <si>
-    <t>income</t>
-  </si>
-  <si>
-    <t>Selected</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>main_score</t>
+    <t>Fine_Scan</t>
+  </si>
+  <si>
+    <t>Pass (IV)</t>
   </si>
   <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>Rough_Scan</t>
-  </si>
-  <si>
-    <t>Pass (IV=0.007)</t>
+    <t>RiskCorr</t>
+  </si>
+  <si>
+    <t>Stable Logic</t>
+  </si>
+  <si>
+    <t>Pass (IV=0.653)</t>
+  </si>
+  <si>
+    <t>Pass (IV=2.297)</t>
   </si>
   <si>
     <t>Pass (IV=0.321)</t>
+  </si>
+  <si>
+    <t>Stable PSI</t>
   </si>
 </sst>
 </file>
@@ -159,8 +192,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:G15" totalsRowShown="0">
-  <autoFilter ref="A1:G15"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Frame0" displayName="Frame0" ref="A1:G29" totalsRowShown="0">
+  <autoFilter ref="A1:G29"/>
   <tableColumns count="7">
     <tableColumn id="1" name="feature" dataDxfId="0"/>
     <tableColumn id="2" name="data_source" dataDxfId="0"/>
@@ -459,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -502,7 +535,7 @@
         <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>0.9982520332325072</v>
       </c>
       <c r="G2" s="1"/>
     </row>
@@ -517,34 +550,34 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2">
-        <v>0.9999681130129501</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F4" s="2">
-        <v>1</v>
+        <v>0.98</v>
       </c>
       <c r="G4" s="1"/>
     </row>
@@ -553,37 +586,37 @@
         <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="2">
-        <v>0.98</v>
+        <v>0.009111436083912849</v>
       </c>
       <c r="G5" s="1"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="F6" s="2">
         <v>0.007448240648955107</v>
@@ -592,192 +625,486 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
-        <v>0.3210684359073639</v>
+        <v>9.462003964126108</v>
       </c>
       <c r="G7" s="1"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8" s="2">
-        <v>0.005833333333333334</v>
+        <v>2.647951126098633</v>
       </c>
       <c r="G8" s="1"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2">
-        <v>0.005833333333333334</v>
+        <v>0.4019330739974976</v>
       </c>
       <c r="G9" s="1"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F10" s="2">
-        <v>0.004833333333333334</v>
+        <v>0.9054592847824097</v>
       </c>
       <c r="G10" s="1"/>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F11" s="2">
-        <v>0.004833333333333334</v>
+        <v>2.647951126098633</v>
       </c>
       <c r="G11" s="1"/>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F12" s="2">
-        <v>0.007448240648955107</v>
+        <v>0.4013484418392181</v>
       </c>
       <c r="G12" s="1"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F13" s="2">
-        <v>0.007448240648955107</v>
+        <v>0.4019330739974976</v>
       </c>
       <c r="G13" s="1"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F14" s="2">
-        <v>0.3210684359073639</v>
+        <v>0.008666666666666666</v>
       </c>
       <c r="G14" s="1"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.008666666666666666</v>
+      </c>
+      <c r="G15" s="1"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0.005833333333333334</v>
+      </c>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F15" s="2">
+      <c r="B17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.005833333333333334</v>
+      </c>
+      <c r="G17" s="1"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.004833333333333334</v>
+      </c>
+      <c r="G18" s="1"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.004833333333333334</v>
+      </c>
+      <c r="G19" s="1"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="2">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.9272727272727272</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.6534533500671387</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="2">
+        <v>2.29707145690918</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.3210684359073639</v>
+      </c>
+      <c r="G25" s="1"/>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F26" s="2">
         <v>0.3209181129932404</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G26" s="1"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.006077066564273531</v>
+      </c>
+      <c r="G27" s="1"/>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.008103952631859824</v>
+      </c>
+      <c r="G28" s="1"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.007753347559946931</v>
+      </c>
+      <c r="G29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/assets/cases/selection.xlsx
+++ b/docs/assets/cases/selection.xlsx
@@ -9229,7 +9229,7 @@
         <v>186</v>
       </c>
       <c r="F416">
-        <v>0.000170720276696734</v>
+        <v>0.0001707202766967335</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -9249,7 +9249,7 @@
         <v>186</v>
       </c>
       <c r="F417">
-        <v>0.0001832998315302326</v>
+        <v>0.0001832998315302324</v>
       </c>
     </row>
     <row r="418" spans="1:6">

--- a/docs/assets/cases/selection.xlsx
+++ b/docs/assets/cases/selection.xlsx
@@ -949,7 +949,7 @@
         <v>134</v>
       </c>
       <c r="F2">
-        <v>0.8823213171880566</v>
+        <v>0.8823213171880598</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -969,7 +969,7 @@
         <v>134</v>
       </c>
       <c r="F3">
-        <v>0.8823213171880566</v>
+        <v>0.8823213171880598</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -989,7 +989,7 @@
         <v>134</v>
       </c>
       <c r="F4">
-        <v>0.8823213171880566</v>
+        <v>0.8823213171880598</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1009,7 +1009,7 @@
         <v>134</v>
       </c>
       <c r="F5">
-        <v>0.8823213171880566</v>
+        <v>0.8823213171880598</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1029,7 +1029,7 @@
         <v>134</v>
       </c>
       <c r="F6">
-        <v>0.8823213171880566</v>
+        <v>0.8823213171880598</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1049,7 +1049,7 @@
         <v>135</v>
       </c>
       <c r="F7">
-        <v>0.8996703591987445</v>
+        <v>0.8996703591987438</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1069,7 +1069,7 @@
         <v>135</v>
       </c>
       <c r="F8">
-        <v>0.8986236516009189</v>
+        <v>0.8986236516009168</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1089,7 +1089,7 @@
         <v>135</v>
       </c>
       <c r="F9">
-        <v>0.8668261346602236</v>
+        <v>0.8668261346602254</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1109,7 +1109,7 @@
         <v>135</v>
       </c>
       <c r="F10">
-        <v>0.8670772483855902</v>
+        <v>0.8670772483855897</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1129,7 +1129,7 @@
         <v>135</v>
       </c>
       <c r="F11">
-        <v>0.8639356117853597</v>
+        <v>0.8639356117853605</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1149,7 +1149,7 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>0.8918696913005881</v>
+        <v>0.8918696913005899</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1169,7 +1169,7 @@
         <v>135</v>
       </c>
       <c r="F13">
-        <v>0.9974113326395556</v>
+        <v>0.9974113326395563</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1189,7 +1189,7 @@
         <v>135</v>
       </c>
       <c r="F14">
-        <v>0.99772194202038</v>
+        <v>0.9977219420203798</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1209,7 +1209,7 @@
         <v>137</v>
       </c>
       <c r="F15">
-        <v>0.99542102278168</v>
+        <v>0.9954210227816792</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1229,7 +1229,7 @@
         <v>137</v>
       </c>
       <c r="F16">
-        <v>0.9963738199389397</v>
+        <v>0.9963738199389401</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1249,7 +1249,7 @@
         <v>138</v>
       </c>
       <c r="F17">
-        <v>0.8256627212152168</v>
+        <v>0.825662721215215</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1269,7 +1269,7 @@
         <v>135</v>
       </c>
       <c r="F18">
-        <v>0.8903995782307512</v>
+        <v>0.8903995782307523</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -1289,7 +1289,7 @@
         <v>135</v>
       </c>
       <c r="F19">
-        <v>0.8902689780398235</v>
+        <v>0.8902689780398243</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -1309,7 +1309,7 @@
         <v>135</v>
       </c>
       <c r="F20">
-        <v>0.8883308083486459</v>
+        <v>0.8883308083486474</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1329,7 +1329,7 @@
         <v>139</v>
       </c>
       <c r="F21">
-        <v>0.8348519297868345</v>
+        <v>0.8348519297868343</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -1349,7 +1349,7 @@
         <v>139</v>
       </c>
       <c r="F22">
-        <v>0.8362414060327832</v>
+        <v>0.8362414060327835</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -1369,7 +1369,7 @@
         <v>140</v>
       </c>
       <c r="F23">
-        <v>0.9552335183895004</v>
+        <v>0.955233518389501</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -1389,7 +1389,7 @@
         <v>135</v>
       </c>
       <c r="F24">
-        <v>0.8964505934136027</v>
+        <v>0.8964505934136034</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -1409,7 +1409,7 @@
         <v>135</v>
       </c>
       <c r="F25">
-        <v>0.8456077943952434</v>
+        <v>0.8456077943952428</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -1429,7 +1429,7 @@
         <v>135</v>
       </c>
       <c r="F26">
-        <v>0.8452747151623707</v>
+        <v>0.8452747151623704</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -1449,7 +1449,7 @@
         <v>135</v>
       </c>
       <c r="F27">
-        <v>0.843009917350579</v>
+        <v>0.8430099173505775</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -9249,7 +9249,7 @@
         <v>186</v>
       </c>
       <c r="F417">
-        <v>0.0001832998315302324</v>
+        <v>0.0001832998315302326</v>
       </c>
     </row>
     <row r="418" spans="1:6">

--- a/docs/assets/cases/selection.xlsx
+++ b/docs/assets/cases/selection.xlsx
@@ -8349,7 +8349,7 @@
         <v>186</v>
       </c>
       <c r="F372">
-        <v>0.0009341831341698193</v>
+        <v>0.0009341831341698172</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -9229,7 +9229,7 @@
         <v>186</v>
       </c>
       <c r="F416">
-        <v>0.0001707202766967335</v>
+        <v>0.000170720276696734</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -9249,7 +9249,7 @@
         <v>186</v>
       </c>
       <c r="F417">
-        <v>0.0001832998315302326</v>
+        <v>0.0001832998315302324</v>
       </c>
     </row>
     <row r="418" spans="1:6">
